--- a/contenu/Troisieme.xlsx
+++ b/contenu/Troisieme.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="16371" yWindow="0" windowWidth="16629" windowHeight="17880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liste" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,18 +19,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -407,7 +401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U179"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
   <cols>
     <col width="2.921875" customWidth="1" style="1" min="1" max="1"/>
@@ -888,13 +882,38 @@
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3.SF1.11</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Reconnaître une situation de proportionnalité par le calcul</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>8N1sCcsG2EY</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>439</v>
+      </c>
       <c r="I12" s="3" t="n"/>
     </row>
     <row r="13" ht="29.15" customHeight="1" s="1">
       <c r="A13" t="n">
         <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
       </c>
       <c r="F13" s="3" t="n"/>
     </row>
@@ -936,163 +955,6 @@
     <row r="22" ht="43.75" customHeight="1" s="1">
       <c r="F22" s="3" t="n"/>
     </row>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -1111,7 +973,8 @@
     <col width="11.07421875" customWidth="1" style="1" min="1" max="1"/>
     <col width="60" customWidth="1" style="1" min="2" max="2"/>
     <col width="2.69140625" customWidth="1" style="1" min="3" max="237"/>
-    <col width="11.07421875" customWidth="1" style="1" min="238" max="16384"/>
+    <col width="11.07421875" customWidth="1" style="1" min="238" max="238"/>
+    <col width="11.07421875" customWidth="1" style="1" min="239" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="59.15" customHeight="1" s="1">
@@ -1992,6 +1855,16 @@
       <c r="H11" s="2" t="n"/>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3.SF1.11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Reconnaître une situation de proportionnalité par le calcul</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="n"/>
     </row>
     <row r="13">
@@ -2662,9 +2535,7 @@
   <dimension ref="A1:AQ16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6"/>
   <cols>
-    <col width="3.69140625" customWidth="1" style="1" min="2" max="16"/>
-    <col width="3.69140625" customWidth="1" style="1" min="17" max="17"/>
-    <col width="3.69140625" customWidth="1" style="1" min="18" max="43"/>
+    <col width="3.69140625" customWidth="1" style="1" min="2" max="43"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/contenu/Troisieme.xlsx
+++ b/contenu/Troisieme.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\Autres ordinateurs\Mon ordinateur portable\Cours\Site\contenu\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxence\Documents\Cours\Site\contenu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5CD87E3-770F-4881-A019-FCF351F44C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B125B7-9DC5-4451-A16D-03DE66F7BF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liste" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="90">
   <si>
     <t>Préfixe</t>
   </si>
@@ -210,6 +210,39 @@
     <t>8N1sCcsG2EY</t>
   </si>
   <si>
+    <t>3.SF2.1</t>
+  </si>
+  <si>
+    <t>Appliquer le théorème de Thales (Papillon)</t>
+  </si>
+  <si>
+    <t>GwGQD2BdZ3s</t>
+  </si>
+  <si>
+    <t>Appliquer le théorème de Thales (Emboité)</t>
+  </si>
+  <si>
+    <t>RwwGbFnvtI4</t>
+  </si>
+  <si>
+    <t>GXMosN4VJWs</t>
+  </si>
+  <si>
+    <t>Appliquer la contraposée du Théorème de Thales</t>
+  </si>
+  <si>
+    <t>fv9pK3hX6b8</t>
+  </si>
+  <si>
+    <t>Appliquer la réciproque du théorème de Thales</t>
+  </si>
+  <si>
+    <t>OaladmqeJ40</t>
+  </si>
+  <si>
+    <t>M4OdnmlFTJs</t>
+  </si>
+  <si>
     <t>x</t>
   </si>
   <si>
@@ -265,36 +298,6 @@
   </si>
   <si>
     <t>Date</t>
-  </si>
-  <si>
-    <t>GwGQD2BdZ3s</t>
-  </si>
-  <si>
-    <t>Appliquer le théorème de Thales (Papillon)</t>
-  </si>
-  <si>
-    <t>RwwGbFnvtI4</t>
-  </si>
-  <si>
-    <t>Appliquer le théorème de Thales (Emboité)</t>
-  </si>
-  <si>
-    <t>Appliquer la contraposée du Théorème de Thales</t>
-  </si>
-  <si>
-    <t>M4OdnmlFTJs</t>
-  </si>
-  <si>
-    <t>GXMosN4VJWs</t>
-  </si>
-  <si>
-    <t>fv9pK3hX6b8</t>
-  </si>
-  <si>
-    <t>Appliquer la réciproque du théorème de Thales</t>
-  </si>
-  <si>
-    <t>OaladmqeJ40</t>
   </si>
 </sst>
 </file>
@@ -621,27 +624,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.921875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4.61328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.4609375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="3.15234375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="44.07421875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="3.3046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="3.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="44.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="3.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="1" customWidth="1"/>
-    <col min="10" max="10" width="2.3046875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="3.921875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="1.921875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="2.765625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="2.3828125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="2.3046875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="2.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="3.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="1.88671875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="2.77734375" style="1" customWidth="1"/>
+    <col min="16" max="17" width="2.33203125" style="1" customWidth="1"/>
     <col min="19" max="19" width="2" style="1" customWidth="1"/>
-    <col min="20" max="20" width="2.23046875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="18.23046875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="2.21875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="18.21875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -706,7 +708,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>3</v>
       </c>
@@ -731,7 +733,7 @@
       <c r="I2" s="3"/>
       <c r="L2" s="3"/>
     </row>
-    <row r="3" spans="1:21" ht="43.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:21" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>3</v>
       </c>
@@ -757,7 +759,7 @@
       <c r="L3" s="3"/>
       <c r="O3" s="3"/>
     </row>
-    <row r="4" spans="1:21" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -780,7 +782,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -805,7 +807,7 @@
       <c r="I5" s="3"/>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="1:21" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -830,7 +832,7 @@
       <c r="I6" s="3"/>
       <c r="L6" s="3"/>
     </row>
-    <row r="7" spans="1:21" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>3</v>
       </c>
@@ -865,7 +867,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>3</v>
       </c>
@@ -889,7 +891,7 @@
       </c>
       <c r="L8" s="3"/>
     </row>
-    <row r="9" spans="1:21" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>3</v>
       </c>
@@ -919,7 +921,7 @@
       </c>
       <c r="L9" s="3"/>
     </row>
-    <row r="10" spans="1:21" ht="43.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:21" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>3</v>
       </c>
@@ -954,7 +956,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>3</v>
       </c>
@@ -983,7 +985,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>3</v>
       </c>
@@ -1007,71 +1009,122 @@
       </c>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" spans="1:21" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>3</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>80</v>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" t="s">
+        <v>61</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
+        <v>62</v>
+      </c>
+      <c r="K13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>3</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>82</v>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" t="s">
+        <v>63</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>81</v>
+        <v>64</v>
+      </c>
+      <c r="H14">
+        <v>277</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
+        <v>65</v>
+      </c>
+      <c r="K14">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>3</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>83</v>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" t="s">
+        <v>66</v>
       </c>
       <c r="F15" s="3"/>
       <c r="I15" s="3"/>
       <c r="L15" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
+        <v>67</v>
+      </c>
+      <c r="N15">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>3</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>87</v>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" t="s">
+        <v>68</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>88</v>
+        <v>69</v>
+      </c>
+      <c r="H16">
+        <v>511</v>
       </c>
       <c r="I16" s="3"/>
       <c r="L16" s="3" t="s">
-        <v>84</v>
+        <v>70</v>
+      </c>
+      <c r="N16">
+        <v>278</v>
       </c>
       <c r="O16" s="3"/>
       <c r="R16" s="3"/>
     </row>
-    <row r="20" spans="6:15" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="6:15" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F20" s="3"/>
       <c r="I20" s="3"/>
       <c r="L20" s="3"/>
       <c r="O20" s="3"/>
     </row>
-    <row r="22" spans="6:15" ht="43.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="6:15" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F22" s="3"/>
     </row>
   </sheetData>
@@ -1083,16 +1136,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:IC230"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.07421875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="60" style="1" customWidth="1"/>
-    <col min="3" max="237" width="2.69140625" style="1" customWidth="1"/>
-    <col min="238" max="239" width="11.07421875" style="1" customWidth="1"/>
-    <col min="240" max="16384" width="11.07421875" style="1"/>
+    <col min="3" max="237" width="2.6640625" style="1" customWidth="1"/>
+    <col min="238" max="240" width="11.109375" style="1" customWidth="1"/>
+    <col min="241" max="16384" width="11.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:237" ht="59.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:237" ht="59.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1805,7 +1858,7 @@
         <v>46570</v>
       </c>
     </row>
-    <row r="2" spans="1:237" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:237" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1813,17 +1866,17 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:237" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:237" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -1831,17 +1884,17 @@
         <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="G3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:237" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:237" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1850,7 +1903,7 @@
       </c>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:237" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:237" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -1859,7 +1912,7 @@
       </c>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:237" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:237" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -1868,7 +1921,7 @@
       </c>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:237" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:237" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -1877,7 +1930,7 @@
       </c>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:237" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:237" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -1886,7 +1939,7 @@
       </c>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:237" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:237" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -1895,7 +1948,7 @@
       </c>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:237" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:237" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -1904,7 +1957,7 @@
       </c>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:237" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:237" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>53</v>
       </c>
@@ -1913,7 +1966,7 @@
       </c>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:237" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:237" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -1922,658 +1975,682 @@
       </c>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:237" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:237" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:237" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:237" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s">
+        <v>63</v>
+      </c>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:237" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:237" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" t="s">
+        <v>66</v>
+      </c>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:237" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:237" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s">
+        <v>68</v>
+      </c>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H18" s="2"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H20" s="2"/>
     </row>
-    <row r="21" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H21" s="2"/>
     </row>
-    <row r="22" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H22" s="2"/>
     </row>
-    <row r="23" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H23" s="2"/>
     </row>
-    <row r="24" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H25" s="2"/>
     </row>
-    <row r="26" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H26" s="2"/>
     </row>
-    <row r="27" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H27" s="2"/>
     </row>
-    <row r="28" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="28" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H30" s="2"/>
     </row>
-    <row r="31" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H31" s="2"/>
     </row>
-    <row r="32" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="32" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H32" s="2"/>
     </row>
-    <row r="33" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="33" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H33" s="2"/>
     </row>
-    <row r="34" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="34" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H34" s="2"/>
     </row>
-    <row r="35" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="35" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H35" s="2"/>
     </row>
-    <row r="36" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="36" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H36" s="2"/>
     </row>
-    <row r="37" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="37" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H37" s="2"/>
     </row>
-    <row r="38" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="38" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="39" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H39" s="2"/>
     </row>
-    <row r="40" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="40" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H40" s="2"/>
     </row>
-    <row r="41" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="41" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H41" s="2"/>
     </row>
-    <row r="42" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="42" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="43" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H43" s="2"/>
     </row>
-    <row r="44" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="44" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H44" s="2"/>
     </row>
-    <row r="45" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="45" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H45" s="2"/>
     </row>
-    <row r="46" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="46" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H46" s="2"/>
     </row>
-    <row r="47" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="47" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H47" s="2"/>
     </row>
-    <row r="48" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="48" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H48" s="2"/>
     </row>
-    <row r="49" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="49" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H49" s="2"/>
     </row>
-    <row r="50" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="50" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H50" s="2"/>
     </row>
-    <row r="51" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="51" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H51" s="2"/>
     </row>
-    <row r="52" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="52" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H52" s="2"/>
     </row>
-    <row r="53" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="53" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H53" s="2"/>
     </row>
-    <row r="54" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="54" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H54" s="2"/>
     </row>
-    <row r="55" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="55" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H55" s="2"/>
     </row>
-    <row r="56" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="56" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="57" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H57" s="2"/>
     </row>
-    <row r="58" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="58" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H58" s="2"/>
     </row>
-    <row r="59" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="59" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H59" s="2"/>
     </row>
-    <row r="60" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="60" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H60" s="2"/>
     </row>
-    <row r="61" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="61" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H61" s="2"/>
     </row>
-    <row r="62" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="62" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H62" s="2"/>
     </row>
-    <row r="63" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="63" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H63" s="2"/>
     </row>
-    <row r="64" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="64" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H64" s="2"/>
     </row>
-    <row r="65" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="65" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H65" s="2"/>
     </row>
-    <row r="66" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="66" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H66" s="2"/>
     </row>
-    <row r="67" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="67" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H67" s="2"/>
     </row>
-    <row r="68" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="68" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H68" s="2"/>
     </row>
-    <row r="69" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="69" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="70" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H70" s="2"/>
     </row>
-    <row r="71" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="71" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H71" s="2"/>
     </row>
-    <row r="72" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="72" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H72" s="2"/>
     </row>
-    <row r="73" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="73" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H73" s="2"/>
     </row>
-    <row r="74" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="74" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H74" s="2"/>
     </row>
-    <row r="75" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="75" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H75" s="2"/>
     </row>
-    <row r="76" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="76" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H76" s="2"/>
     </row>
-    <row r="77" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="77" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H77" s="2"/>
     </row>
-    <row r="78" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="78" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H78" s="2"/>
     </row>
-    <row r="79" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="79" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H79" s="2"/>
     </row>
-    <row r="80" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="80" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H80" s="2"/>
     </row>
-    <row r="81" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="81" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H81" s="2"/>
     </row>
-    <row r="82" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="82" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H82" s="2"/>
     </row>
-    <row r="83" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="83" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="84" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H84" s="2"/>
     </row>
-    <row r="85" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="85" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H85" s="2"/>
     </row>
-    <row r="86" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="86" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H86" s="2"/>
     </row>
-    <row r="87" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="87" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H87" s="2"/>
     </row>
-    <row r="88" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="88" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H88" s="2"/>
     </row>
-    <row r="89" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="89" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H89" s="2"/>
     </row>
-    <row r="90" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="90" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H90" s="2"/>
     </row>
-    <row r="91" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="91" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H91" s="2"/>
     </row>
-    <row r="92" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="92" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H92" s="2"/>
     </row>
-    <row r="93" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="93" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H93" s="2"/>
     </row>
-    <row r="94" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="94" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H94" s="2"/>
     </row>
-    <row r="95" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="95" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H95" s="2"/>
     </row>
-    <row r="96" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="96" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H96" s="2"/>
     </row>
-    <row r="97" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="97" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H97" s="2"/>
     </row>
-    <row r="98" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="98" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H98" s="2"/>
     </row>
-    <row r="99" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="99" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H99" s="2"/>
     </row>
-    <row r="100" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="100" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H100" s="2"/>
     </row>
-    <row r="101" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="101" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H101" s="2"/>
     </row>
-    <row r="102" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="102" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H102" s="2"/>
     </row>
-    <row r="103" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="103" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H103" s="2"/>
     </row>
-    <row r="104" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="104" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H104" s="2"/>
     </row>
-    <row r="105" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="105" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H105" s="2"/>
     </row>
-    <row r="106" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="106" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H106" s="2"/>
     </row>
-    <row r="107" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="107" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H107" s="2"/>
     </row>
-    <row r="108" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="108" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H108" s="2"/>
     </row>
-    <row r="109" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="109" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H109" s="2"/>
     </row>
-    <row r="110" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="110" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H110" s="2"/>
     </row>
-    <row r="111" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="111" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H111" s="2"/>
     </row>
-    <row r="112" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="112" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H112" s="2"/>
     </row>
-    <row r="113" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="113" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H113" s="2"/>
     </row>
-    <row r="114" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="114" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H114" s="2"/>
     </row>
-    <row r="115" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="115" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H115" s="2"/>
     </row>
-    <row r="116" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="116" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H116" s="2"/>
     </row>
-    <row r="117" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="117" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H117" s="2"/>
     </row>
-    <row r="118" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="118" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H118" s="2"/>
     </row>
-    <row r="119" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="119" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H119" s="2"/>
     </row>
-    <row r="120" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="120" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H120" s="2"/>
     </row>
-    <row r="121" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="121" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H121" s="2"/>
     </row>
-    <row r="122" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="122" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H122" s="2"/>
     </row>
-    <row r="123" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="123" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H123" s="2"/>
     </row>
-    <row r="124" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="124" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H124" s="2"/>
     </row>
-    <row r="125" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="125" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H125" s="2"/>
     </row>
-    <row r="126" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="126" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H126" s="2"/>
     </row>
-    <row r="127" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="127" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H127" s="2"/>
     </row>
-    <row r="128" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="128" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H128" s="2"/>
     </row>
-    <row r="129" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="129" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H129" s="2"/>
     </row>
-    <row r="130" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="130" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H130" s="2"/>
     </row>
-    <row r="131" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="131" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H131" s="2"/>
     </row>
-    <row r="132" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="132" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H132" s="2"/>
     </row>
-    <row r="133" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="133" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H133" s="2"/>
     </row>
-    <row r="134" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="134" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H134" s="2"/>
     </row>
-    <row r="135" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="135" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H135" s="2"/>
     </row>
-    <row r="136" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="136" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H136" s="2"/>
     </row>
-    <row r="137" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="137" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H137" s="2"/>
     </row>
-    <row r="138" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="138" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H138" s="2"/>
     </row>
-    <row r="139" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="139" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H139" s="2"/>
     </row>
-    <row r="140" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="140" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H140" s="2"/>
     </row>
-    <row r="141" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="141" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H141" s="2"/>
     </row>
-    <row r="142" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="142" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H142" s="2"/>
     </row>
-    <row r="143" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="143" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H143" s="2"/>
     </row>
-    <row r="144" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="144" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H144" s="2"/>
     </row>
-    <row r="145" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="145" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H145" s="2"/>
     </row>
-    <row r="146" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="146" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H146" s="2"/>
     </row>
-    <row r="147" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="147" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H147" s="2"/>
     </row>
-    <row r="148" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="148" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H148" s="2"/>
     </row>
-    <row r="149" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="149" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H149" s="2"/>
     </row>
-    <row r="150" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="150" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H150" s="2"/>
     </row>
-    <row r="151" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="151" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H151" s="2"/>
     </row>
-    <row r="152" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="152" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H152" s="2"/>
     </row>
-    <row r="153" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="153" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H153" s="2"/>
     </row>
-    <row r="154" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="154" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H154" s="2"/>
     </row>
-    <row r="155" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="155" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H155" s="2"/>
     </row>
-    <row r="156" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="156" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H156" s="2"/>
     </row>
-    <row r="157" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="157" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H157" s="2"/>
     </row>
-    <row r="158" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="158" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H158" s="2"/>
     </row>
-    <row r="159" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="159" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H159" s="2"/>
     </row>
-    <row r="160" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="160" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H160" s="2"/>
     </row>
-    <row r="161" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="161" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H161" s="2"/>
     </row>
-    <row r="162" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="162" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H162" s="2"/>
     </row>
-    <row r="163" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="163" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H163" s="2"/>
     </row>
-    <row r="164" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="164" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H164" s="2"/>
     </row>
-    <row r="165" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="165" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H165" s="2"/>
     </row>
-    <row r="166" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="166" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H166" s="2"/>
     </row>
-    <row r="167" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="167" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H167" s="2"/>
     </row>
-    <row r="168" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="168" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H168" s="2"/>
     </row>
-    <row r="169" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="169" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H169" s="2"/>
     </row>
-    <row r="170" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="170" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H170" s="2"/>
     </row>
-    <row r="171" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="171" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H171" s="2"/>
     </row>
-    <row r="172" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="172" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H172" s="2"/>
     </row>
-    <row r="173" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="173" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H173" s="2"/>
     </row>
-    <row r="174" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="174" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H174" s="2"/>
     </row>
-    <row r="175" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="175" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H175" s="2"/>
     </row>
-    <row r="176" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="176" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H176" s="2"/>
     </row>
-    <row r="177" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="177" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H177" s="2"/>
     </row>
-    <row r="178" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="178" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H178" s="2"/>
     </row>
-    <row r="179" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="179" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H179" s="2"/>
     </row>
-    <row r="180" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="180" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H180" s="2"/>
     </row>
-    <row r="181" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="181" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H181" s="2"/>
     </row>
-    <row r="182" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="182" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H182" s="2"/>
     </row>
-    <row r="183" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="183" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H183" s="2"/>
     </row>
-    <row r="184" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="184" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H184" s="2"/>
     </row>
-    <row r="185" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="185" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H185" s="2"/>
     </row>
-    <row r="186" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="186" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H186" s="2"/>
     </row>
-    <row r="187" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="187" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H187" s="2"/>
     </row>
-    <row r="188" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="188" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H188" s="2"/>
     </row>
-    <row r="189" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="189" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H189" s="2"/>
     </row>
-    <row r="190" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="190" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H190" s="2"/>
     </row>
-    <row r="191" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="191" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H191" s="2"/>
     </row>
-    <row r="192" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="192" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H192" s="2"/>
     </row>
-    <row r="193" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="193" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H193" s="2"/>
     </row>
-    <row r="194" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="194" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H194" s="2"/>
     </row>
-    <row r="195" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="195" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H195" s="2"/>
     </row>
-    <row r="196" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="196" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H196" s="2"/>
     </row>
-    <row r="197" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="197" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H197" s="2"/>
     </row>
-    <row r="198" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="198" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H198" s="2"/>
     </row>
-    <row r="199" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="199" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H199" s="2"/>
     </row>
-    <row r="200" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="200" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H200" s="2"/>
     </row>
-    <row r="201" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="201" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H201" s="2"/>
     </row>
-    <row r="202" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="202" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H202" s="2"/>
     </row>
-    <row r="203" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="203" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H203" s="2"/>
     </row>
-    <row r="204" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="204" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H204" s="2"/>
     </row>
-    <row r="205" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="205" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H205" s="2"/>
     </row>
-    <row r="206" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="206" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H206" s="2"/>
     </row>
-    <row r="207" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="207" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H207" s="2"/>
     </row>
-    <row r="208" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="208" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H208" s="2"/>
     </row>
-    <row r="209" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="209" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H209" s="2"/>
     </row>
-    <row r="210" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="210" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H210" s="2"/>
     </row>
-    <row r="211" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="211" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H211" s="2"/>
     </row>
-    <row r="212" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="212" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H212" s="2"/>
     </row>
-    <row r="213" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="213" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H213" s="2"/>
     </row>
-    <row r="214" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="214" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H214" s="2"/>
     </row>
-    <row r="215" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="215" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H215" s="2"/>
     </row>
-    <row r="216" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="216" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H216" s="2"/>
     </row>
-    <row r="217" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="217" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H217" s="2"/>
     </row>
-    <row r="218" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="218" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H218" s="2"/>
     </row>
-    <row r="219" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="219" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H219" s="2"/>
     </row>
-    <row r="220" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="220" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H220" s="2"/>
     </row>
-    <row r="221" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="221" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H221" s="2"/>
     </row>
-    <row r="222" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="222" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H222" s="2"/>
     </row>
-    <row r="223" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="223" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H223" s="2"/>
     </row>
-    <row r="224" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="224" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H224" s="2"/>
     </row>
-    <row r="225" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="225" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H225" s="2"/>
     </row>
-    <row r="226" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="226" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H226" s="2"/>
     </row>
-    <row r="227" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="227" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H227" s="2"/>
     </row>
-    <row r="228" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="228" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H228" s="2"/>
     </row>
-    <row r="229" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="229" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H229" s="2"/>
     </row>
-    <row r="230" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="230" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H230" s="2"/>
     </row>
   </sheetData>
@@ -2584,12 +2661,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AQ16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="43" width="3.69140625" style="1" customWidth="1"/>
+    <col min="2" max="43" width="3.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.3">
       <c r="B1">
         <v>37</v>
       </c>
@@ -2609,10 +2686,10 @@
         <v>42</v>
       </c>
       <c r="H1" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="I1" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="J1">
         <v>45</v>
@@ -2636,10 +2713,10 @@
         <v>51</v>
       </c>
       <c r="Q1" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="R1" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="S1">
         <v>1</v>
@@ -2660,10 +2737,10 @@
         <v>6</v>
       </c>
       <c r="Y1" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="Z1" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="AA1">
         <v>9</v>
@@ -2684,10 +2761,10 @@
         <v>14</v>
       </c>
       <c r="AG1" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="AH1" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="AI1">
         <v>17</v>
@@ -2717,79 +2794,79 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.4">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.4">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.4">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.4">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.4">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2800,17 +2877,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>37</v>
       </c>
@@ -2818,7 +2895,7 @@
         <v>46272</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>37</v>
       </c>
@@ -2826,7 +2903,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>37</v>
       </c>
@@ -2834,7 +2911,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>37</v>
       </c>
@@ -2842,7 +2919,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>37</v>
       </c>
@@ -2850,7 +2927,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>37</v>
       </c>
@@ -2858,7 +2935,7 @@
         <v>46277</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>37</v>
       </c>
@@ -2866,7 +2943,7 @@
         <v>46278</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>38</v>
       </c>
@@ -2874,7 +2951,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>38</v>
       </c>
@@ -2882,7 +2959,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>38</v>
       </c>
@@ -2890,7 +2967,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>38</v>
       </c>
@@ -2898,7 +2975,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>38</v>
       </c>
@@ -2906,7 +2983,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>38</v>
       </c>
@@ -2914,7 +2991,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>38</v>
       </c>

--- a/contenu/Troisieme.xlsx
+++ b/contenu/Troisieme.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Liste" sheetId="1" state="visible" r:id="rId1"/>
@@ -401,7 +401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U22"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.21875" defaultRowHeight="14.4"/>
   <cols>
     <col width="2.88671875" customWidth="1" style="1" min="1" max="1"/>
@@ -1067,18 +1067,195 @@
       <c r="O16" s="3" t="n"/>
       <c r="R16" s="3" t="n"/>
     </row>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3.SF3.1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Simple distributivité</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SH1hQrsZGsk</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>263</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>YS-3JI_z2f0</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3.SF3.2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Double distributivité</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>o6qVMmA3oTQ</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>275</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>hly4i9QDUT0</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3.SF3.3</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Identité remarquable (a+b)² = a²+2ab + b² et (a-b)² = a²-2ab + b²</t>
+        </is>
+      </c>
+    </row>
     <row r="20" ht="29.1" customHeight="1" s="1">
+      <c r="A20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3.SF3.4</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Identité remarquable (a-b)(a+b)</t>
+        </is>
+      </c>
       <c r="F20" s="3" t="n"/>
       <c r="I20" s="3" t="n"/>
       <c r="L20" s="3" t="n"/>
       <c r="O20" s="3" t="n"/>
     </row>
-    <row r="21"/>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Factoriser</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1OOl4u2kIg8</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>769</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>UGTFELhE9Dw</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>351</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>08peWLwhIzc</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>327</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>ujBZ1luBUJE</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>242</v>
+      </c>
+    </row>
     <row r="22" ht="43.8" customHeight="1" s="1">
+      <c r="A22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
       <c r="F22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1098,8 +1275,8 @@
     <col width="11.109375" customWidth="1" style="1" min="1" max="1"/>
     <col width="60" customWidth="1" style="1" min="2" max="2"/>
     <col width="2.6640625" customWidth="1" style="1" min="3" max="237"/>
-    <col width="11.109375" customWidth="1" style="1" min="238" max="242"/>
-    <col width="11.109375" customWidth="1" style="1" min="243" max="16384"/>
+    <col width="11.109375" customWidth="1" style="1" min="238" max="243"/>
+    <col width="11.109375" customWidth="1" style="1" min="244" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="59.1" customHeight="1" s="1">
@@ -2045,15 +2222,55 @@
       <c r="H16" s="2" t="n"/>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3.SF3.1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Simple distributivité</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="n"/>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3.SF3.2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Double distributivité</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="n"/>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3.SF3.3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Identité remarquable (a+b)² = a²+2ab + b² et (a-b)² = a²-2ab + b²</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="n"/>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3.SF3.4</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Identité remarquable (a-b)(a+b)</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="n"/>
     </row>
     <row r="21">
